--- a/catalogs/PYTHON_MODULE_CATALOG.xlsx
+++ b/catalogs/PYTHON_MODULE_CATALOG.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PYTHON_MODULE_CATALOG" sheetId="1" r:id="Rb531c9e6359e4b60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PYTHON_MODULE_CATALOG" sheetId="1" r:id="R9f598a76dce24c6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,7 +30,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -52,6 +52,11 @@
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF6B2436"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -60,7 +65,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -99,6 +104,10 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -328,70 +337,70 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="45" customHeight="1">
-      <x:c r="A1" s="9" t="str">
+      <x:c r="A1" s="17" t="str">
         <x:v>resource_id</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="17" t="str">
         <x:v>module_number</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="17" t="str">
         <x:v>title</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="17" t="str">
         <x:v>primary_chapter</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="E1" s="17" t="str">
         <x:v>primary_chapter_title</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="F1" s="17" t="str">
         <x:v>additional_chapters</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="G1" s="17" t="str">
         <x:v>related_core_resources</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="H1" s="17" t="str">
         <x:v>related_case</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="str">
+      <x:c r="I1" s="17" t="str">
         <x:v>formats</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="J1" s="17" t="str">
         <x:v>version</x:v>
       </x:c>
-      <x:c r="K1" s="9" t="str">
+      <x:c r="K1" s="17" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="L1" s="9" t="str">
+      <x:c r="L1" s="17" t="str">
         <x:v>folder</x:v>
       </x:c>
-      <x:c r="M1" s="9" t="str">
+      <x:c r="M1" s="17" t="str">
         <x:v>primary_related_case</x:v>
       </x:c>
-      <x:c r="N1" s="9" t="str">
+      <x:c r="N1" s="17" t="str">
         <x:v>additional_related_cases</x:v>
       </x:c>
-      <x:c r="O1" s="9" t="str">
+      <x:c r="O1" s="17" t="str">
         <x:v>related_cases</x:v>
       </x:c>
-      <x:c r="P1" s="9" t="str">
+      <x:c r="P1" s="17" t="str">
         <x:v>script_path</x:v>
       </x:c>
-      <x:c r="Q1" s="9" t="str">
+      <x:c r="Q1" s="17" t="str">
         <x:v>notebook_path</x:v>
       </x:c>
-      <x:c r="R1" s="9" t="str">
+      <x:c r="R1" s="17" t="str">
         <x:v>xlsx_template_path</x:v>
       </x:c>
-      <x:c r="S1" s="9" t="str">
+      <x:c r="S1" s="17" t="str">
         <x:v>ods_template_path</x:v>
       </x:c>
-      <x:c r="T1" s="9" t="str">
+      <x:c r="T1" s="17" t="str">
         <x:v>example_outputs_path</x:v>
       </x:c>
-      <x:c r="U1" s="9" t="str">
+      <x:c r="U1" s="17" t="str">
         <x:v>release_date</x:v>
       </x:c>
-      <x:c r="V1" s="9" t="str">
+      <x:c r="V1" s="17" t="str">
         <x:v>safeguard</x:v>
       </x:c>
     </x:row>
@@ -421,7 +430,7 @@
         <x:v>AIHE-CASE02</x:v>
       </x:c>
       <x:c r="I2" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J2" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -483,7 +492,7 @@
         <x:v>AIHE-CASE05</x:v>
       </x:c>
       <x:c r="I3" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J3" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -545,7 +554,7 @@
         <x:v>AIHE-CASE02</x:v>
       </x:c>
       <x:c r="I4" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J4" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -607,7 +616,7 @@
         <x:v>AIHE-CASE11</x:v>
       </x:c>
       <x:c r="I5" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J5" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -669,7 +678,7 @@
         <x:v>AIHE-CASE11</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J6" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -731,7 +740,7 @@
         <x:v>AIHE-CASE03</x:v>
       </x:c>
       <x:c r="I7" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -793,7 +802,7 @@
         <x:v>AIHE-CASE10</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J8" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -855,7 +864,7 @@
         <x:v>AIHE-CASE10</x:v>
       </x:c>
       <x:c r="I9" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J9" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -917,7 +926,7 @@
         <x:v>AIHE-CASE12</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J10" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -979,7 +988,7 @@
         <x:v>AIHE-CASE06</x:v>
       </x:c>
       <x:c r="I11" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J11" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -1041,7 +1050,7 @@
         <x:v>AIHE-CASE06</x:v>
       </x:c>
       <x:c r="I12" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J12" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -1103,7 +1112,7 @@
         <x:v>AIHE-CASE07</x:v>
       </x:c>
       <x:c r="I13" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J13" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -1165,7 +1174,7 @@
         <x:v>AIHE-CASE07</x:v>
       </x:c>
       <x:c r="I14" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J14" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -1227,7 +1236,7 @@
         <x:v>AIHE-CASE08</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J15" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -1289,7 +1298,7 @@
         <x:v>AIHE-CASE08</x:v>
       </x:c>
       <x:c r="I16" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -1351,7 +1360,7 @@
         <x:v>AIHE-CASE07</x:v>
       </x:c>
       <x:c r="I17" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J17" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -1413,7 +1422,7 @@
         <x:v>AIHE-CASE09</x:v>
       </x:c>
       <x:c r="I18" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J18" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -1475,7 +1484,7 @@
         <x:v>AIHE-CASE08</x:v>
       </x:c>
       <x:c r="I19" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J19" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -1537,7 +1546,7 @@
         <x:v>AIHE-CASE08</x:v>
       </x:c>
       <x:c r="I20" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J20" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -1599,7 +1608,7 @@
         <x:v>AIHE-CASE08</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J21" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -1661,7 +1670,7 @@
         <x:v>AIHE-CASE03</x:v>
       </x:c>
       <x:c r="I22" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J22" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -1725,7 +1734,7 @@
         <x:v>AIHE-CASE04</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -1787,7 +1796,7 @@
         <x:v>AIHE-CASE04</x:v>
       </x:c>
       <x:c r="I24" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J24" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -1851,7 +1860,7 @@
         <x:v>AIHE-CASE11</x:v>
       </x:c>
       <x:c r="I25" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -1913,7 +1922,7 @@
         <x:v>AIHE-CASE09</x:v>
       </x:c>
       <x:c r="I26" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J26" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -1975,7 +1984,7 @@
         <x:v>AIHE-CASE10</x:v>
       </x:c>
       <x:c r="I27" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J27" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -2037,7 +2046,7 @@
         <x:v>AIHE-CASE12</x:v>
       </x:c>
       <x:c r="I28" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J28" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -2099,7 +2108,7 @@
         <x:v>AIHE-CASE04</x:v>
       </x:c>
       <x:c r="I29" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J29" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -2223,7 +2232,7 @@
         <x:v>AIHE-CASE11</x:v>
       </x:c>
       <x:c r="I31" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J31" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -2285,7 +2294,7 @@
         <x:v>AIHE-CASE11</x:v>
       </x:c>
       <x:c r="I32" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J32" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -2347,7 +2356,7 @@
         <x:v>AIHE-CASE11</x:v>
       </x:c>
       <x:c r="I33" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J33" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -2409,7 +2418,7 @@
         <x:v>AIHE-CASE02</x:v>
       </x:c>
       <x:c r="I34" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J34" s="12" t="str">
         <x:v>V1.0</x:v>
@@ -2471,7 +2480,7 @@
         <x:v>AIHE-CASE03</x:v>
       </x:c>
       <x:c r="I35" s="14" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J35" s="14" t="str">
         <x:v>V1.0</x:v>
@@ -2535,7 +2544,7 @@
         <x:v>AIHE-CASE03</x:v>
       </x:c>
       <x:c r="I36" s="12" t="str">
-        <x:v>py; ipynb; xlsx; csv; json; png; md</x:v>
+        <x:v>xlsx; py; ipynb; csv; json; md; png</x:v>
       </x:c>
       <x:c r="J36" s="12" t="str">
         <x:v>V1.0</x:v>
